--- a/data/trans_dic/IP24_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que no hacen ejercicio</t>
+          <t>Menores que no hacen ejercicio (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,94; 31,65</t>
+          <t>19,52; 31,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,4; 24,53</t>
+          <t>13,49; 24,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,82; 30,59</t>
+          <t>17,33; 29,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,38; 20,32</t>
+          <t>10,6; 19,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,19; 29,45</t>
+          <t>17,73; 29,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,6; 20,52</t>
+          <t>11,13; 20,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,38; 19,39</t>
+          <t>9,47; 19,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,12; 39,08</t>
+          <t>11,96; 40,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,37; 28,45</t>
+          <t>20,21; 28,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,24; 20,44</t>
+          <t>13,03; 20,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,76; 22,47</t>
+          <t>14,57; 22,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,09; 29,39</t>
+          <t>12,77; 28,51</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,97; 33,25</t>
+          <t>23,23; 33,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,33; 26,61</t>
+          <t>17,09; 26,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,99; 25,87</t>
+          <t>17,06; 25,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,52; 29,87</t>
+          <t>15,12; 29,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,75; 28,03</t>
+          <t>19,2; 28,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,08; 19,98</t>
+          <t>12,24; 20,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,78; 24,08</t>
+          <t>15,25; 23,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,09; 20,71</t>
+          <t>12,96; 21,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,31; 28,73</t>
+          <t>22,36; 29,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,83; 21,93</t>
+          <t>15,89; 21,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,21; 23,11</t>
+          <t>17,4; 23,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,19; 22,51</t>
+          <t>14,67; 22,44</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,93; 28,6</t>
+          <t>17,78; 28,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,01; 27,81</t>
+          <t>17,07; 27,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,13; 26,78</t>
+          <t>17,11; 27,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,85; 60,2</t>
+          <t>21,52; 58,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,0; 25,52</t>
+          <t>14,68; 25,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,89; 22,74</t>
+          <t>13,46; 23,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,96; 20,15</t>
+          <t>11,31; 19,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,07; 29,3</t>
+          <t>17,34; 29,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,51; 25,11</t>
+          <t>17,6; 25,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,36; 23,14</t>
+          <t>16,24; 23,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,14; 21,81</t>
+          <t>15,27; 21,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,89; 45,39</t>
+          <t>21,96; 44,33</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,76; 30,11</t>
+          <t>20,33; 30,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,67; 24,29</t>
+          <t>15,0; 24,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,56; 26,91</t>
+          <t>17,69; 27,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 24,32</t>
+          <t>13,79; 25,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,78; 32,15</t>
+          <t>22,01; 31,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,01; 19,18</t>
+          <t>11,25; 19,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,33; 22,39</t>
+          <t>13,14; 21,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,43; 18,02</t>
+          <t>9,18; 17,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,94; 29,21</t>
+          <t>22,27; 29,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,21; 20,34</t>
+          <t>13,92; 20,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,66; 23,37</t>
+          <t>16,47; 23,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,87; 19,61</t>
+          <t>12,94; 19,43</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,8; 28,02</t>
+          <t>22,61; 27,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,08; 22,89</t>
+          <t>17,9; 22,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,51; 24,36</t>
+          <t>19,45; 24,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,13; 35,05</t>
+          <t>18,92; 35,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,97; 26,0</t>
+          <t>20,94; 26,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,83; 18,31</t>
+          <t>13,63; 18,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 19,0</t>
+          <t>14,83; 19,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,33; 22,47</t>
+          <t>15,31; 22,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,42; 26,13</t>
+          <t>22,42; 26,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,22; 19,69</t>
+          <t>16,49; 19,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,64; 21,0</t>
+          <t>17,73; 21,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,87; 25,8</t>
+          <t>17,75; 25,91</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que no hacen ejercicio (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>34556</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24981</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30965</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17241</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35312</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23391</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20576</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>28872</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>69869</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48372</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>51541</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>46113</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>26790; 43527</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18579; 34045</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23054; 39177</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12390; 23163</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>27142; 44779</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>16936; 31828</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13918; 28071</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>16733; 56516</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>58690; 83266</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>37760; 59766</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>40804; 63279</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>32781; 73198</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>54188</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>44578</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43826</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40049</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>49692</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>35153</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>43336</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>41390</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>103880</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>79731</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>87161</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>81439</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>45343; 64636</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>35153; 54185</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>35354; 53770</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>28804; 56017</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>40736; 59959</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>27157; 45102</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>34115; 53633</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>32880; 53565</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>91072; 118754</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>67930; 93235</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>74981; 101418</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>65177; 99670</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>31129</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33802</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>33783</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>66418</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29577</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29737</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>25272</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>41357</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>60706</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>63539</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>59056</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>107775</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>24397; 39189</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26354; 41970</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>26699; 43263</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>40797; 110048</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>21964; 37634</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>22332; 38639</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>18778; 33085</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>31705; 53479</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>50482; 72095</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>52008; 75870</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>49181; 70334</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>81804; 165109</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>51857</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40090</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>45792</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31687</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54292</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>30165</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>35220</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>23882</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>106149</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>70255</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>81012</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>55569</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>42550; 63276</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31187; 51007</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>36572; 56508</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>23014; 41758</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>45450; 64512</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>22829; 38952</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>26782; 44122</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>16646; 32404</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>92580; 121501</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>57209; 85099</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>67628; 95013</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>45030; 67622</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>171730</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>143451</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>154366</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>155395</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>168873</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>118446</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>124404</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>135501</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>340603</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>261896</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>278770</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>290896</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>153497; 189808</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>126335; 161135</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>136754; 171778</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>125608; 237866</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>151063; 188270</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>101268; 134647</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>109816; 142331</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>116013; 169253</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>313924; 366474</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>238919; 285448</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>255880; 304123</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>252371; 368345</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP24_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,52; 31,71</t>
+          <t>19,59; 31,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,49; 24,73</t>
+          <t>13,05; 24,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,33; 29,45</t>
+          <t>17,41; 30,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,6; 19,81</t>
+          <t>10,25; 20,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,73; 29,25</t>
+          <t>18,0; 29,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,13; 20,91</t>
+          <t>11,15; 21,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,47; 19,09</t>
+          <t>9,57; 19,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,96; 40,4</t>
+          <t>12,14; 41,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,21; 28,68</t>
+          <t>20,02; 28,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,03; 20,62</t>
+          <t>12,92; 20,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,57; 22,6</t>
+          <t>14,87; 22,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,77; 28,51</t>
+          <t>13,08; 28,78</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,23; 33,12</t>
+          <t>22,71; 33,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,09; 26,34</t>
+          <t>17,68; 26,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 25,94</t>
+          <t>17,22; 25,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,12; 29,4</t>
+          <t>15,14; 29,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,2; 28,26</t>
+          <t>18,97; 28,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,24; 20,33</t>
+          <t>11,84; 19,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,25; 23,97</t>
+          <t>15,51; 24,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,96; 21,11</t>
+          <t>12,52; 20,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,36; 29,16</t>
+          <t>22,34; 28,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,89; 21,8</t>
+          <t>15,87; 21,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,4; 23,53</t>
+          <t>17,06; 23,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,67; 22,44</t>
+          <t>15,38; 22,79</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,78; 28,57</t>
+          <t>17,5; 28,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,07; 27,19</t>
+          <t>17,09; 27,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,11; 27,73</t>
+          <t>16,84; 26,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,52; 58,05</t>
+          <t>21,89; 62,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,68; 25,15</t>
+          <t>14,99; 25,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,46; 23,28</t>
+          <t>13,54; 23,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,31; 19,93</t>
+          <t>11,6; 20,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,34; 29,24</t>
+          <t>16,94; 29,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,6; 25,13</t>
+          <t>17,58; 25,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,24; 23,69</t>
+          <t>16,74; 23,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,27; 21,84</t>
+          <t>15,11; 22,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,96; 44,33</t>
+          <t>21,87; 43,91</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,33; 30,23</t>
+          <t>19,77; 30,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,0; 24,53</t>
+          <t>14,79; 24,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,69; 27,33</t>
+          <t>17,67; 27,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,79; 25,03</t>
+          <t>13,58; 24,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,01; 31,25</t>
+          <t>21,34; 31,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,25; 19,19</t>
+          <t>11,33; 19,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,14; 21,65</t>
+          <t>13,51; 21,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,18; 17,88</t>
+          <t>9,6; 18,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,27; 29,22</t>
+          <t>21,67; 29,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,92; 20,71</t>
+          <t>14,15; 20,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,47; 23,14</t>
+          <t>16,81; 23,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,94; 19,43</t>
+          <t>12,73; 19,78</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,61; 27,96</t>
+          <t>22,76; 27,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,9; 22,83</t>
+          <t>17,86; 22,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,45; 24,43</t>
+          <t>19,44; 24,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,92; 35,83</t>
+          <t>18,78; 34,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,94; 26,1</t>
+          <t>20,85; 25,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 18,12</t>
+          <t>13,65; 18,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,83; 19,22</t>
+          <t>14,58; 18,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,31; 22,34</t>
+          <t>15,28; 22,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,42; 26,17</t>
+          <t>22,45; 26,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,49; 19,7</t>
+          <t>16,42; 19,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,73; 21,07</t>
+          <t>17,7; 20,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,75; 25,91</t>
+          <t>17,68; 25,51</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26790; 43527</t>
+          <t>26886; 43161</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18579; 34045</t>
+          <t>17962; 33397</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23054; 39177</t>
+          <t>23164; 40064</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12390; 23163</t>
+          <t>11984; 23781</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27142; 44779</t>
+          <t>27557; 44975</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16936; 31828</t>
+          <t>16964; 32493</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13918; 28071</t>
+          <t>14064; 29123</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16733; 56516</t>
+          <t>16986; 57988</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58690; 83266</t>
+          <t>58113; 81587</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37760; 59766</t>
+          <t>37463; 60202</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40804; 63279</t>
+          <t>41631; 63414</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32781; 73198</t>
+          <t>33582; 73915</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45343; 64636</t>
+          <t>44314; 64733</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35153; 54185</t>
+          <t>36375; 54956</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35354; 53770</t>
+          <t>35689; 53340</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28804; 56017</t>
+          <t>28850; 55665</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40736; 59959</t>
+          <t>40235; 59696</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27157; 45102</t>
+          <t>26261; 44219</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34115; 53633</t>
+          <t>34703; 53989</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32880; 53565</t>
+          <t>31770; 52693</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91072; 118754</t>
+          <t>90993; 118046</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67930; 93235</t>
+          <t>67859; 93137</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74981; 101418</t>
+          <t>73512; 100392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65177; 99670</t>
+          <t>68299; 101247</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24397; 39189</t>
+          <t>24013; 38703</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26354; 41970</t>
+          <t>26384; 43154</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26699; 43263</t>
+          <t>26270; 41790</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40797; 110048</t>
+          <t>41509; 118019</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21964; 37634</t>
+          <t>22431; 38336</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22332; 38639</t>
+          <t>22469; 38373</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18778; 33085</t>
+          <t>19247; 33461</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31705; 53479</t>
+          <t>30984; 53759</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50482; 72095</t>
+          <t>50432; 71989</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52008; 75870</t>
+          <t>53626; 75359</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49181; 70334</t>
+          <t>48663; 70824</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>81804; 165109</t>
+          <t>81443; 163562</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42550; 63276</t>
+          <t>41372; 63176</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31187; 51007</t>
+          <t>30770; 50141</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36572; 56508</t>
+          <t>36535; 56294</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23014; 41758</t>
+          <t>22664; 41509</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45450; 64512</t>
+          <t>44061; 64516</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22829; 38952</t>
+          <t>22990; 39475</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26782; 44122</t>
+          <t>27533; 44557</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16646; 32404</t>
+          <t>17407; 33705</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>92580; 121501</t>
+          <t>90113; 121138</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57209; 85099</t>
+          <t>58142; 84444</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67628; 95013</t>
+          <t>69008; 95811</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45030; 67622</t>
+          <t>44310; 68836</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>153497; 189808</t>
+          <t>154519; 189953</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>126335; 161135</t>
+          <t>126031; 160032</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136754; 171778</t>
+          <t>136692; 172716</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>125608; 237866</t>
+          <t>124635; 229313</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>151063; 188270</t>
+          <t>150375; 187450</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>101268; 134647</t>
+          <t>101381; 136456</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>109816; 142331</t>
+          <t>108004; 139898</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>116013; 169253</t>
+          <t>115769; 168429</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>313924; 366474</t>
+          <t>314300; 366319</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>238919; 285448</t>
+          <t>237913; 284186</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>255880; 304123</t>
+          <t>255509; 302504</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>252371; 368345</t>
+          <t>251372; 362673</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP24_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23,07%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15,37%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19,47%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>25,17%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>18,14%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>23,28%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,07%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,59; 31,44</t>
+          <t>18,19; 29,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,05; 24,26</t>
+          <t>10,6; 20,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,41; 30,12</t>
+          <t>9,38; 19,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,25; 20,34</t>
+          <t>11,66; 36,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,0; 29,38</t>
+          <t>19,94; 31,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,15; 21,35</t>
+          <t>13,4; 24,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,57; 19,81</t>
+          <t>17,82; 30,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,14; 41,45</t>
+          <t>9,16; 18,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,02; 28,1</t>
+          <t>20,37; 28,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,92; 20,77</t>
+          <t>13,24; 20,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,87; 22,64</t>
+          <t>14,76; 22,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,08; 28,78</t>
+          <t>12,02; 26,38</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23,42%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15,84%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19,37%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>27,77%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>21,67%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>21,15%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21,02%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>23,42%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15,84%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,37%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,71; 33,17</t>
+          <t>18,75; 28,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,68; 26,71</t>
+          <t>12,08; 19,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,22; 25,74</t>
+          <t>15,78; 24,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,14; 29,22</t>
+          <t>10,15; 17,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 28,14</t>
+          <t>22,97; 33,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,84; 19,93</t>
+          <t>17,33; 26,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,51; 24,13</t>
+          <t>16,99; 25,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,52; 20,77</t>
+          <t>12,83; 21,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,34; 28,98</t>
+          <t>22,31; 28,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,87; 21,78</t>
+          <t>15,83; 21,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 23,29</t>
+          <t>17,21; 23,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,38; 22,79</t>
+          <t>12,51; 18,03</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,76%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17,92%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15,23%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>22,69%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>21,9%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>21,66%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>35,03%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,5; 28,21</t>
+          <t>15,0; 25,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,09; 27,96</t>
+          <t>12,89; 22,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,84; 26,79</t>
+          <t>10,96; 20,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,89; 62,25</t>
+          <t>15,72; 27,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,99; 25,62</t>
+          <t>17,93; 28,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,54; 23,12</t>
+          <t>17,01; 27,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,6; 20,16</t>
+          <t>17,13; 26,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,94; 29,4</t>
+          <t>17,33; 29,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,58; 25,1</t>
+          <t>17,51; 25,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,74; 23,53</t>
+          <t>16,36; 23,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,11; 22,0</t>
+          <t>15,14; 21,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,87; 43,91</t>
+          <t>18,1; 26,71</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26,29%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14,86%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17,28%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13,82%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>24,77%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>19,28%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>22,15%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18,99%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>26,29%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,28%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,77; 30,18</t>
+          <t>21,78; 32,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,79; 24,11</t>
+          <t>11,01; 19,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,67; 27,23</t>
+          <t>13,33; 22,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 24,88</t>
+          <t>10,13; 18,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,34; 31,25</t>
+          <t>19,76; 30,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 19,45</t>
+          <t>14,67; 24,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,51; 21,86</t>
+          <t>17,56; 26,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 18,6</t>
+          <t>13,07; 22,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,67; 29,13</t>
+          <t>21,94; 29,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,15; 20,55</t>
+          <t>14,21; 20,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,81; 23,34</t>
+          <t>16,66; 23,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,73; 19,78</t>
+          <t>12,56; 19,01</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23,41%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15,94%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>25,29%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>20,33%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>21,96%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>15,94%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,76; 27,98</t>
+          <t>20,97; 26,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,86; 22,68</t>
+          <t>13,83; 18,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,44; 24,57</t>
+          <t>14,58; 19,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,78; 34,54</t>
+          <t>14,19; 20,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,85; 25,99</t>
+          <t>22,8; 28,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,65; 18,37</t>
+          <t>18,08; 22,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 18,89</t>
+          <t>19,51; 24,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,28; 22,23</t>
+          <t>15,46; 20,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,45; 26,16</t>
+          <t>22,42; 26,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,42; 19,62</t>
+          <t>16,22; 19,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,7; 20,96</t>
+          <t>17,64; 21,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,68; 25,51</t>
+          <t>15,43; 19,39</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35312</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23391</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20576</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24438</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>34556</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>24981</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>30965</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17241</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>35312</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23391</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20576</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28872</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46113</t>
+          <t>40435</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26886; 43161</t>
+          <t>27852; 45089</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17962; 33397</t>
+          <t>16138; 31234</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23164; 40064</t>
+          <t>13784; 28511</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11984; 23781</t>
+          <t>14630; 45206</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27557; 44975</t>
+          <t>27375; 43447</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16964; 32493</t>
+          <t>18452; 33779</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14064; 29123</t>
+          <t>23709; 40694</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16986; 57988</t>
+          <t>11061; 22252</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58113; 81587</t>
+          <t>59139; 82595</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37463; 60202</t>
+          <t>38375; 59256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41631; 63414</t>
+          <t>41344; 62929</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33582; 73915</t>
+          <t>29604; 64964</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>49692</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35153</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43336</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32536</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>54188</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>44578</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>43826</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>40049</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>49692</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>35153</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>43336</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41390</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81439</t>
+          <t>63569</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44314; 64733</t>
+          <t>39781; 59459</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36375; 54956</t>
+          <t>26812; 44321</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35689; 53340</t>
+          <t>35312; 53871</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28850; 55665</t>
+          <t>23939; 41649</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40235; 59696</t>
+          <t>44828; 64896</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26261; 44219</t>
+          <t>35655; 54742</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34703; 53989</t>
+          <t>35212; 53619</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31770; 52693</t>
+          <t>23668; 40051</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90993; 118046</t>
+          <t>90857; 117014</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67859; 93137</t>
+          <t>67690; 93778</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73512; 100392</t>
+          <t>74192; 99599</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68299; 101247</t>
+          <t>52589; 75791</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>29577</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29737</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25272</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34957</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>31129</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>33802</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>33783</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>66418</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>29577</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>29737</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>25272</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41357</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>107775</t>
+          <t>70957</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24013; 38703</t>
+          <t>22446; 38197</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26384; 43154</t>
+          <t>21390; 37734</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26270; 41790</t>
+          <t>18194; 33444</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41509; 118019</t>
+          <t>26161; 45846</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22431; 38336</t>
+          <t>24598; 39235</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22469; 38373</t>
+          <t>26260; 42930</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19247; 33461</t>
+          <t>26722; 41784</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30984; 53759</t>
+          <t>27071; 46523</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50432; 71989</t>
+          <t>50237; 72038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53626; 75359</t>
+          <t>52419; 74116</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48663; 70824</t>
+          <t>48740; 70229</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>81443; 163562</t>
+          <t>58404; 86164</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>54292</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30165</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35220</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23414</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>51857</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>40090</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>45792</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31687</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>54292</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>30165</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>35220</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>29057</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55569</t>
+          <t>52470</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41372; 63176</t>
+          <t>44975; 66377</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30770; 50141</t>
+          <t>22341; 38923</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36535; 56294</t>
+          <t>27175; 45637</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22664; 41509</t>
+          <t>17151; 31636</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44061; 64516</t>
+          <t>41368; 63018</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22990; 39475</t>
+          <t>30505; 50519</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27533; 44557</t>
+          <t>36305; 55642</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17407; 33705</t>
+          <t>21724; 37514</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>90113; 121138</t>
+          <t>91222; 121459</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58142; 84444</t>
+          <t>58375; 83570</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69008; 95811</t>
+          <t>68411; 95936</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44310; 68836</t>
+          <t>42158; 63790</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>185</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>168873</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>118446</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>124404</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>115344</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>171730</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>143451</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>154366</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>155395</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>168873</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>118446</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>124404</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>154519; 189953</t>
+          <t>151269; 187574</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>126031; 160032</t>
+          <t>102726; 136006</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136692; 172716</t>
+          <t>107953; 140703</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>124635; 229313</t>
+          <t>98906; 144738</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>150375; 187450</t>
+          <t>154794; 190240</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>101381; 136456</t>
+          <t>127592; 161534</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>108004; 139898</t>
+          <t>137167; 171263</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>115769; 168429</t>
+          <t>97037; 128550</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>314300; 366319</t>
+          <t>313929; 365840</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>237913; 284186</t>
+          <t>235037; 285202</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>255509; 302504</t>
+          <t>254577; 303220</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>251372; 362673</t>
+          <t>204352; 256861</t>
         </is>
       </c>
     </row>
